--- a/data/exports/王颖瑜伽/dist_order_2026-10-09.xlsx
+++ b/data/exports/王颖瑜伽/dist_order_2026-10-09.xlsx
@@ -324,7 +324,7 @@
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>春华秋实</t>
+          <t>老张</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
